--- a/excel_file/Объявление.xlsx
+++ b/excel_file/Объявление.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -502,1132 +502,6346 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Названия товара</t>
+          <t>Смартфон Vivo Y04, 4/64 ГБ, 4/128 ГБ, IP64, 90 Гц, 5500 мА/ч</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>Цена</t>
+          <t>1 247 040</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Ссылка</t>
+          <t>https://uzum.uz/ru/product/smartfon-vivo-y04-zelenyj---120-1649861</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Доп информация</t>
+          <t>4.8 (34 отзыва)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Tecno Smartphone Tecno Spark Go (2025) Rostest (EAC) 3/ 128 GB, black</t>
+          <t>Смартфон Xiaomi Redmi A5 4GB 128GB, дисплей 6.88" IPS, 32mp камера, 5200 mAh</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>591 107 UZS</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/tecno-smartfon-spark-go-1-rostest-eac-3-128-gb-chernyy-2071234646/?at=Y7tjEjoBNIYEXBlniNn1mmNT2KGv7OsXq0Kv0SXr8k8K</t>
+          <t>939 840</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-xiaomi-redmi-chernyj---1-1623426</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>4.8 (411 отзыв)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Apple Smartphone Apple iPhone 13 4/ 256 GB, pink, Refurbished</t>
+          <t>Смартфон Xiaomi Redmi A5 4GB 128GB, дисплей 6.88" IPS, 32mp камера, 5200 mAh</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>5 123 033 UZS</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/vosstanovlennyy-apple-smartfon-iphone-13-4-256-gb-rozovyy-1873609144/?at=GRt2K2ZX0uLQgYYLFVZwvRWTp10l6GTQwLWGku404P20</t>
+          <t>939 840</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-xiaomi-redmi-goluboj---127-1623426</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.8 (411 отзыв)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Smartphone 4Good Kids S45 Global 12/ 512 GB, black</t>
+          <t>Смартфон W&amp;O X25 Ultra — 8 ГБ ОЗУ, 128 ГБ ПЗУ, камера 26 МП, 6,8-дюймовый HD-экран</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>932 791 UZS</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/smartfon-smartfon-global-edition-cmartfon-i16-pro-max-modnyy-umnyy-mobilnyy-telefon-razvlecheniya-2323671737/?at=gpt4O45QmUZYZ02VuXXWyxPfxypz2EI68M52ZIyjpAxj</t>
+          <t>1 112 640</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-wo-x25-chernyj---1-1858173</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>Новинка!</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Apple Smartphone Apple iPhone 15 6/ 256 GB, light blue, Refurbished</t>
+          <t>Смартфон Samsung Galaxy A16 8/256 ГБ, 6/128 ГБ, 2 SIM 50 Мп, SUPER AMOLED</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>7 672 461 UZS</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/vosstanovlennyy-apple-smartfon-iphone-15-6-256-gb-goluboy-2446053168/?at=vQtrpr0V2t51WmBxC6lgRoWcXAGyA2h4WNYjAcAZk7YL</t>
+          <t>1 938 240</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-seryj-metallik---291-1349626</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.9 (4243 отзыва)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>iQOO Smartphone iQOO Z10 Lite Rostest (EAC) 8/ 256 GB, green</t>
+          <t>Смартфон Samsung Galaxy A16 8/256 ГБ, 6/128 ГБ, 2 SIM 50 Мп, SUPER AMOLED</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>1 818 497 UZS</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/iqoo-smartfon-z10-lite-rostest-eac-8-256-gb-zelenyy-2467156597/?at=A6tGLGJqncO3kyv0uPmvRwBTgWlB48TEjvJXohWzYXQX</t>
+          <t>1 938 240</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-chernyj---1-1349626</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>4.9 (4243 отзыва)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Poco Smartphone Poco C61 3/ 64 GB, black</t>
+          <t>Смартфон ZTE Blade A75 5G 4/128 5000mAh/ 2025</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>642 805 UZS</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/poco-smartfon-poco-c61-3-64-gb-chernyy-1687012093/?at=J8tg3gLM1hpRpY0tZx0OBPcLqKWRrCXG64yvUOY59Xw</t>
+          <t>1 391 990</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-zte-blade-a75-5g-4128-1858160</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>Новинка!</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>SHOWJI Smartphone 360 F4 EU 16/ 512 GB, white</t>
+          <t>OPPO A5x4+128GB 45W 6000mhA IP65</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>1 472 995 UZS</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/showji-smartfon-smartfon-5g-16gb-512gb-ultradolgovechnyy-akkumulyator-5500mah-2329531034/?at=XQtkVk7rqc2xBVYXcAmAjW4Tr0jPKZF5LJyknc6PXx2O</t>
+          <t>1 142 400</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/oppo-a5x4128gb-45w-6000mha-ip65-indigo---251-1869267</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>It has become cheaper</t>
+          <t>5.0 (1 отзыв)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Febimel Smartphone 24/ 512 GB, grey</t>
+          <t>Смартфон Redmi Note 14, 8GB+256GB, AMOLED 120Hz дисплей, 6.67"</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>1 107 610 UZS</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/febimel-smartfon-smartfon-mobilnyy-telefon-s25-ultra-smartfon-24-512-gb-seryy-2070356179/?at=J8tg3gLM1hnlwk5wCRQmzxyhgrOOLBsxMxGy1FXMom8Q</t>
+          <t>2 303 040</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-redmi-note-chernyj---1-1481304</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>It has become cheaper</t>
+          <t>4.8 (435 отзывов)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>iQOO Smartphone iQOO Z10 Lite Rostest (EAC) 8/ 128 GB, green</t>
+          <t>Смартфон Infinix Smart 9, 3/64GB, 4/128GB, 5000 mAh, 6.7'', 120 Гц</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>1 671 038 UZS</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/iqoo-smartfon-z10-lite-rostest-eac-8-128-gb-zelenyy-2467171218/?at=Z8tXrXnBDUxvvOjguyv7N4EFwVMYY7CZMRq9WF2rRk06</t>
+          <t>907 190</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-smart-biryuzovyj---124-1265840</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>4.7 (125 отзывов)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>iQOO Smartphone iQOO Z10 Rostest (EAC) 8/ 256 GB, metallic grey</t>
+          <t>Смартфон Samsung Galaxy A16 8/256 ГБ, 6/128 ГБ, 2 SIM 50 Мп, SUPER AMOLED</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2 300 004 UZS</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/iqoo-smartfon-z10-rostest-eac-8-256-gb-seryy-metallik-2132949943/?at=r2t4P43J1UNLEMPDFWpJ2EGCvDoJ1pc9Kp5kLTzA6o1r</t>
+          <t>1 938 240</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-myatnyj---123-1349626</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>4.9 (4243 отзыва)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>iQOO Smartphone iQOO Z10 Rostest (EAC) 12/ 512 GB, black</t>
+          <t>Ударопрочный смартфон HONOR X9C Smart, 120 Гц, 5800 мА/ч, 108 Мп</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>2 887 294 UZS</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/iqoo-smartfon-z10-rostest-eac-12-512-gb-chernyy-2133542381/?at=LZtlylM8mI1YpZkvfxXJ7J9U0yXBpsplODOkTv0NW8j</t>
+          <t>2 591 040</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/udaroprochnyj-smartfon-honor-chernyj---1-1479003</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>4.6 (85 отзывов)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>iQOO Smartphone iQOO Neo 10 Rostest (EAC) 12/ 256 GB, orange</t>
+          <t>Смартфон Redmi Note 14 pro, 12GB+512GB, AMOLED 120Hz дисплей</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>3 720 665 UZS</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/iqoo-smartfon-neo-10-rostest-eac-12-256-gb-oranzhevyy-krasnyy-2132947705/?at=jYtZKZ1N3UVGB8GJfyqDjAVhrPxl4Yfjk0r8YTZ4j1GE</t>
+          <t>3 647 040</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-redmi-note-chernyj---1-1436235</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>4.8 (72 отзыва)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Tecno Smartphone Rostest (EAC) 8/ 256 GB, black</t>
+          <t>Смартфон Infinix HOT 60 Pro+, 8/256 ГБ, изогнутый 3D AMOLED экран 144Гц, 50 МП, 5160 мА/ч, 45 Вт</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>2 390 356 UZS</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/tecno-smartfon-pova-7-neo-rostest-eac-8-256-gb-chernyy-2316774535/?at=jYtZKZ1N3Uq8NRoZTg7m74AUnDqM2EfjYygpwuNRr9r5</t>
+          <t>2 880 000</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-hot-seryj-metallik---291-1873143</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>5.0 (1 отзыв)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Tecno Smartphone Tecno Pova 7 Neo Rostest (EAC) 8/ 256 GB, black</t>
+          <t>Смартфон Tecno Spark Go 1, 3+3/128 ГБ</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2 260 555 UZS</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/tecno-smartfon-pova-7-neo-rostest-eac-8-256-gb-chernyy-cherno-seryy-2353104536/?at=OgtEzErQ0uBgVXjmsl4KnRQu18D8P4h60kr96c25r8yz</t>
+          <t>959 040</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-tecno-spark-go-1-33128-chernyj---1-1710354</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>It has become cheaper</t>
+          <t>4.8 (43 отзыва)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Tecno Smartphone Tecno Pova 6 Rostest (EAC) 12/ 256 GB, grey</t>
+          <t>Смартфон Infinix HOT 50 8/128 ГБ, 8/256 ГБ, 120 Ghz, IP54, MediaTek G100</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>2 467 029 UZS</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/tecno-smartfon-pova-6-rostest-eac-12-256-gb-seryy-1861593994/?at=pZtp1pE6vfpmP17pIzRRoEjuEMNE4JSqx9gVzhW9jM9z</t>
+          <t>1 793 270</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-hot-chernyj---1-1253435</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>4.8 (133 отзыва)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Tecno Smartphone Tecno Camon 30S Rostest (EAC) 8/ 128 GB, black</t>
+          <t>Смартфон Infinix HOT 50 - 60 Pro Plus</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>2 377 472 UZS</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/tecno-smartfon-camon-30s-rostest-eac-8-128-gb-chernyy-1713665988/?at=J8tg3gLM1hnA0NYOFlyYoKJf5G0KVkTgRrqG2fk5QE9X</t>
+          <t>2 601 590</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-hot-50-60-pro-rozovyj---16-1336878</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>4.8 (73 отзыва)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Xiaomi Smartphone Redmi 14C 8/ 256 GB, blue</t>
+          <t>Смартфон Infinix Note 50 Pro, 12+12/256Гб, AMOLED 144Гц, 5200mAч 90W, беспроводная зарядка</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>1 443 408 UZS</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/xiaomi-smartfon-redmi-14c-8-256-gb-siniy-1726508104/?at=z6tOQONVxcMzYmnrsyO9jORS1NG566IMVAZ1KI3E6J6o</t>
+          <t>3 263 040</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-note-chernyj---1-1654787</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>4.8 (205 отзывов)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Redmi Smartphone Redmi 14C CN 8/ 256 GB, black, Refurbished</t>
+          <t>Смартфон Xiaomi Redmi 15, бонусные Bluetooth-наушники TWS M10, 7000 мАч 33 Вт, 144Гц, 50МП</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>932 632 UZS</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/vosstanovlennyy-redmi-smartfon-cn-8-256-gb-chernyy-1875740738/?at=6WtZjZlw1Ujk6NVYFQJZMDWiQD6WNjUO2pBN9tO32OgE</t>
+          <t>2 111 040</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-xiaomi-redmi-chernyj---1-1872231</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>Новинка!</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Tecno Smartphone Tecno Pova 7 Neo Rostest (EAC) 8/ 256 GB, copper</t>
+          <t>Смартфон Honor 400 Lite 5G 8/256 Гб, 108 МП улучшенная камера с ИИ, AMOLED дисплей 5230мАч</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>2 299 845 UZS</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/tecno-smartfon-pova-7-neo-rostest-eac-8-256-gb-med-2352362241/?at=LZtlylM8mIk9nkrosK8Zlz6uvNwXRXImrM8A7IQRQz04</t>
+          <t>3 157 440</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-honor-400-seryj---3-1680333</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>4.6 (78 отзывов)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Apple Smartphone Apple iPad Air (2024) 8/ 1 TB, black</t>
+          <t>Смартфон W&amp;O X 25 ультра 8/128 ГБ</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>25 063 191 UZS</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/apple-smartfon-iphone-16-pro-max-black-8-1-tb-chernyy-1990533706/?at=PjtJ8JAVocP0yD1ZuN0VK2zfQ8qn5BTBMPqY8sknZlEQ</t>
+          <t>1 195 200</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-wo-x-25-ultra-8128-zolotoj---133-1631642</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>3.3 (319 отзывов)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>realme Smartphone realme C71 Rostest (EAC) 6/ 128 GB, green</t>
+          <t>Смартфон Xiaomi Poco X7 Pro, 12GB+512GB, 6,67" AMOLED 120Hz дисплей, 6000 мА/ч, 5G</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>1 285 769 UZS</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/realme-smartfon-c71-rostest-eac-6-128-gb-zelenyy-2157514329/?at=z6tOQONVxcvnmmj8f0YNYMriRQmlJ9fJnLO1LfyZ33zA</t>
+          <t>4 415 040</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-xiaomi-poco-zheltyj---118-1465653</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>5.0 (10 отзывов)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Tecno Smartphone Tecno Camon 40 Premier Rostest (EAC) 12/ 256 GB, black</t>
+          <t>Смартфон W&amp;O X 25 ультра 8/128 ГБ</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>5 375 956 UZS</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/tecno-smartfon-camon-40-premier-5g-8-yader-3-5-ggts-amoled-1260x2800-144gts-kamera-50mp-ois-2043242503/?at=WPtNRNwoPUKWQnBWHZRR3yBUMj7lx4sL0MBngt6W090J</t>
+          <t>1 195 200</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-wo-x-25-ultra-8128-seryj---3-1631642</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>3.3 (319 отзывов)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>realme Smartphone 512 GB, green</t>
+          <t>Смартфон W&amp;O X 16 8/128 ГБ, X 15 pro max 4/64 ГБ</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>2 277 893 UZS</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/realme-smartfon-512-gb-zelenyy-1627130557/?at=r2t4P43J1UjAqk2vioKymMKTEyzNjOs3GmlBQsp323AG</t>
+          <t>958 080</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-wo-x-16-8128-gb-belyj---5-1487310</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>3.5 (1120 отзывов)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Tecno Smartphone Tecno Camon 40 Pro 5G Rostest (EAC) 8/ 256 GB, black</t>
+          <t>Смартфон Redmi Note 14, 8 GB+256 GB, AMOLED 120Hz дисплей, 6.67"</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>3 296 265 UZS</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/tecno-smartfon-camon-40-pro-5g-rostest-eac-8-256-gb-chernyy-2006925399/?at=ywtAqAmV0hLp2B4LIZEJ9rc03PjRWI0lVN1yfNpz3r6</t>
+          <t>2 111 040</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-redmi-note-chernyj---1-1436848</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>4.8 (1210 отзывов)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Febimel Smartphone 4Good S450m 16/ 1 TB, black</t>
+          <t>Смартфон Tecno Spark 30C, 4+4/128 ГБ</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>1 107 610 UZS</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/febimel-smartfon-telefon-i15-promax-chernyy-16-1-tb-chernyy-2390541286/?at=pZtp1pE6vfpZ92r6t7G0owjUOlZwy5u0DADNYtnvnKY4</t>
+          <t>1 343 040</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-tecno-spark-30c-44128-gb-chernyj---1-1835838</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>5.0 (6 отзывов)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Xiaomi Smartphone Redmi 13C 8/ 256 GB, white, Refurbished</t>
+          <t>Смартфон Infinix HOT 60 Pro+ 8/256 ГБ изогнутый 3D AMOLED экран 144Гц 50 МП 5160 мАч 45 Вт</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>845 143 UZS</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/vosstanovlennyy-xiaomi-smartfon-8-256-gb-belyy-2007615212/?at=XQtkVk7rqcVB8mBLfrVXBpqum7YLYKIVv1VvQf2K1o8V</t>
+          <t>2 879 040</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-hot-chernyj---1-1401116</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.9 (138 отзывов)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>FRBBY Smartphone 4/ 128 GB, green</t>
+          <t>Смартфон Infinix Smart 10, 4+4/128 ГБ</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>722 659 UZS</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/frbby-smartfon-smartfon-f20-4gb-128gb-5000mah-4-128-gb-zelenyy-1656369509/?at=OgtEzErQ0uljvmNZc632BMKfLgp186iBWXGWmhE4LPG9</t>
+          <t>997 440</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-smart-10-44128-gb-zolotoj---133-1835407</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.0 (3 отзыва)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Tecno Smartphone Tecno Spark Go (2025) Rostest (EAC) 3/ 128 GB, white</t>
+          <t>Смартфон Redmi 15C, 8/256 ГБ, 6.9" IPS 120 Гц, 50 Мп, MediaTek Helio G81 Ultra, 6000 мА/ч</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>753 359 UZS</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/tecno-smartfon-spark-go-1-rostest-eac-3-128-gb-belyy-2071234654/?at=GRt2K2ZX0uYvxY4jhrv1rQlTlpyvjKSYYyEqrFK8l2n0</t>
+          <t>1 609 920</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-redmi-15c-pesochnyj---1021-1879391</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>Новинка!</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>M-HORSE Smartphone 4/ 128 GB, gold</t>
+          <t>Смартфон Samsung Galaxy A06,5000мАч,быстрая 25Вт,камера 50Мп,2 SIM-карты,гарантия 1 год</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>833 372 UZS</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/m-horse-smartfon-a14-4-128-gb-zolotoy-1664034098/?at=nRtrArpBKt4VBmyyCz9OR5Dim6llnwcgYrDp1HAL0pv5</t>
+          <t>1 343 040</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-belyj---5-1305234</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>5.0 (2 отзыва)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Samsung Smartphone Samsung Galaxy S24 FE 8/ 128 GB, dark grey</t>
+          <t>Смартфон Realme Note 60x, 4+8/128 ГБ</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>6 105 613 UZS</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/samsung-smartfon-galaxy-s24-fe-global-8-128-gb-temno-seryy-1706740140/?at=DqtDNDrGnumz4OqvF6z8xQjIOnvw7tqBrWpPsRNkmgL</t>
+          <t>1 055 040</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-realme-note-60x-48128-gb-chernyj---1-1785638</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>4.4 (19 отзывов)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Poco Smartphone Poco X7 Pro Rostest (EAC) 12/ 512 GB, black</t>
+          <t>Смартфон Infinix Smart 10, 4+4/128 ГБ</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>4 582 352 UZS</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/poco-smartfon-poco-x7-pro-podderzhka-nfc-rostest-eac-12-512-gb-chernyy-1896512902/?at=79tn4nj7QfqDAxwWuKvplWrTP596ZGcy722wPS6JLO56</t>
+          <t>1 099 200</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-smart-10-44128-gb-chernyj---1-1835407</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>It has become cheaper</t>
+          <t>5.0 (3 отзыва)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Apple Smartphone Apple iPhone 16 Pro 8/ 256 GB, grey</t>
+          <t>Смартфон Samsung Galaxy A36 5G</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>15 852 834 UZS</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/apple-smartfon-iphone-16-pro-esim-sim-8-256-gb-seryy-1687844335/?at=QktJMJ4Z3cKDAVM3uJ308ADtBr5JWGSWGQBPmtkorM88</t>
+          <t>3 935 040</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-a36-5g-chernyj---1-1602772</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>4.9 (87 отзывов)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Tecno Smartphone Rostest (EAC) 12/ 256 GB, black</t>
+          <t>Смартфон MBO 16PRO MAX 8/128 ГБ</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>2 546 087 UZS</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/tecno-smartfon-camon-40-rostest-eac-12-256-gb-chernyy-2267934742/?at=oZt6j6pWBhjWWNjKCOKWXVxfr62l3kcYv1RnpsB1nB33</t>
+          <t>1 343 040</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-mbo-16pro-max-8128-gb-oranzhevyj---18-1823360</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>3.7 (19 отзывов)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Hotwav Smartphone Hotwav Hyper 7 Pro Rostest (EAC) 16/ 256 GB, black</t>
+          <t>Смартфон Infinix Smart 9 HD, 3+3/64 ГБ</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>3 481 900 UZS</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/hotwav-smartfon-smartfon-hotwav-hyper-7-pro-120hz-10-5-mp-2-sim-ip68-android-14-16-20-256-gb-1928486919/?at=nRtrArpBKtNBz6nyH7Gp8MJSo3B7yPfnKNYPBFLqzj9q</t>
+          <t>997 440</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-smart-9-hd-3364-chernyj---1-1730262</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.7 (29 отзывов)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Xiaomi Smartphone Poco F7 Rostest (EAC) 12/ 512 GB, silvery</t>
+          <t>Смартфон Infinix GT 30 Pro 5G, 12+12/256gb, AMOLED 144Hz, 120FPS, 5500mAh 45w + подарок</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>5 547 911 UZS</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/xiaomi-smartfon-poco-f7-rostest-eac-12-512-gb-serebristyy-2246262950/?at=99trLrV7MtxqONmjHvm80vuMg8WnWi5k3Zy4cGrD5m5</t>
+          <t>5 183 040</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-gt-chernyj---1-1779911</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>4.7 (10 отзывов)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Honor Smartphone Honor 400 Lite Rostest (EAC) 8/ 256 GB, green</t>
+          <t>Смартфон Redmi Note 14 Pro, 12GB+512GB, AMOLED 120Hz дисплей</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>3 213 230 UZS</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/honor-smartfon-400-lite-rostest-eac-8-256-gb-zelenyy-2133657498/?at=QktJMJ4Z3c2Rvj66FEjDEWwSBqWWZTroGPooHwPOjG</t>
+          <t>3 497 280</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-redmi-note-chernyj---1-1434945</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>4.7 (72 отзыва)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Xiaomi Smartphone 3/ 64 GB, gold</t>
+          <t>Смартфон Ajib i10 128 ГБ + чехол и защитное стекло</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>779 924 UZS</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/xiaomi-smartfon-redmi-a5-3-64-gb-zolotoy-1998926880/?at=XQtkVk7rqc0z3R75Cv2WPv6c006z9vhwk79Eycnl9Ev4</t>
+          <t>863 040</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-ajib-i10-128-gb-chekhol-chernyj---1-1688208</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>4.5 (94 отзыва)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Febimel Smartphone 16/ 1 TB, black</t>
+          <t>Смартфон Xiaomi Redmi 15, 7000 мАч 33 Вт, 144Гц, 50 МП</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>1 107 610 UZS</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/febimel-smartfon-s24-ultra-j6-stilnyy-mobilnyy-telefon-sensornyy-android-16-1-tb-chernyy-2388140423/?at=XQtkVk7rqc7QBBZ2cvw4jRjTGK1jolSPYKYnvuEwnJgN</t>
+          <t>2 060 160</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-xiaomi-redmi-chernyj---1-1873540</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>Новинка!</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Smartphone 4Good S600m Global 12/ 512 GB, matte black</t>
+          <t>Смартфон Xiaomi Redmi 14C, 8+256ГБ, 5160 мА/ч батарея, быстрая зарядка 18W, камера 50МП AI</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>932 791 UZS</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/smartfon-rossiyskaya-versiya-4g-6-5-hd-ekran-zashchita-ot-vody-i-udarov-moshchnyy-dlya-igr-gibkie-2392287817/?at=28t0P0oyRuGkQYMGS6BKJPgcEjxGK6IO1Y8ADcQXxXEN</t>
+          <t>1 525 440</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-xiaomi-redmi-chernyj---1-1245393</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8 (1102 отзыва)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Poco Smartphone Poco M7 Pro Rostest (EAC) 8/ 256 GB, lilac</t>
+          <t>Смартфон Infinix Note 50 Pro, 12+12/256Гб, AMOLED 144Гц, 5200mAч 90W, беспроводная зарядка</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>2 295 709 UZS</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/poco-smartfon-m7-pro-rostest-eac-8-256-gb-sirenevyy-1952922882/?at=K8tZzZxpBUrA3M7OFJwOJkBTv00kRxSNZYpD2ckxV3JV</t>
+          <t>3 263 040</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-note-seryj---3-1654787</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>4.8 (205 отзывов)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Redmi Smartphone Redmi 14C CN 8/ 256 GB, blue, Refurbished</t>
+          <t>Мини смартфон S25 Ultra, сенсорный телефон, Android 12, с памятью 2/16 Гб</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>932 632 UZS</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/vosstanovlennyy-redmi-smartfon-cn-8-256-gb-siniy-1875178032/?at=79tn4nj7QfRZVY6qHQzjRg6ilykR9rIO0ny0gUolypRg</t>
+          <t>672 000</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/mini-smartfon-s25-chernyj---1-1851680</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>5.0 (7 отзывов)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Smartphone 4/ 128 GB, light blue</t>
+          <t>Смартфон W&amp;O X 16 8/128 ГБ</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>636 601 UZS</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/smartfon-j206-4-128-gb-goluboy-1859545169/?at=Y7tjEjoBNI2XEr0JtmqPE4whX0rlW1ivjpM74HmoVg74</t>
+          <t>1 151 040</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-wo-x-16-8128-gb-zolotoj---133-1618160</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>3.5 (287 отзывов)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>vove Smartphone Rostest (EAC) 16/ 1 TB, matte black</t>
+          <t>Смартфон Infinix Note 50, 8+8/256 ГБ</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>1 406 981 UZS</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/vove-smartfon-2025-novyy-android-smartfon-s18-pro-16-1024gb-5000-mach-android-13-50mp-50mp-2394259496/?at=lRt606q4AhGMqDLDSZEL8RWTr8V3AoH6RA718HADPxrL</t>
+          <t>3 071 040</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-note-50-88256-gb-bezhevyj-melanzh---249-1745015</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>4.6 (11 отзывов)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Xiaomi Smartphone Rostest (EAC) 3/ 64 GB, black</t>
+          <t>Смартфон Honor X6c, 6+256ГБ, с 120Гц экраном, 5300мАч батарея, 35Вт зарядка, 50МП камера</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>779 924 UZS</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/xiaomi-smartfon-redmi-a5-rostest-eac-3-64-gb-chernyy-1998926897/?at=k2to8o3Gru2PkM0EsAE3Al6FK76r08HEwY4MWF65y0J7</t>
+          <t>1 631 040</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-honor-x6c-chernyj---1-1768915</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Original</t>
+          <t>4.8 (9 отзывов)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Vivo Smartphone Rostest (EAC) 4/ 128 GB, dark green</t>
+          <t>Смартфон Redmi 15C, 8/256 ГБ, 6.9" IPS 120 Гц, 50 Мп, MediaTek Helio G81 Ultra, 6000 мА/ч</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>936 927 UZS</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/vivo-smartfon-y04-rostest-eac-4-128-gb-temno-zelenyy-1950282279/?at=k2to8o3GruxNZRNpi66jD5OfEGOQzrfYM48G9hzmxzmo</t>
+          <t>1 609 920</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-redmi-15c-chernyj---1-1879391</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>It has become cheaper</t>
+          <t>Новинка!</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>M-HORSE Smartphone Tecno Spark 20 Pro Rostest (EAC) 4/ 64 GB, olive green</t>
+          <t>Смартфон Xiaomi Poco C71, 4+128ГБ, 32 Мп двойная камера, 6,88" дисплей</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>687 027 UZS</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/m-horse-smartfon-tecno-smartfon-spark-30-rostest-eac-8-128-gb-belyy-rostest-eac-4-64-gb-olivkovyy-1921961169/?at=BrtzpzJ2MI6EX3RxTOv0Qz9U0XN0pQIVkWnnMcqB7Vlq</t>
+          <t>1 055 040</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-xiaomi-poco-goluboj---127-1797693</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.8 (5 отзывов)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Febimel Smartphone 16/ 1 TB, black</t>
+          <t>Смартфон Huawei nova 11i 8/128 ГБ</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>1 107 610 UZS</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/febimel-smartfon-mate60-16-1-tb-chernyy-2390540888/?at=w0tgJgZrAhQlDXPpSGpJD7xUExPX1Duzk30AYf39Yzx6</t>
+          <t>1 287 360</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-huawei-nova-11i-8128-gb-chernyj---1-1835101</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.7 (6 отзывов)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Xiaomi Smartphone Redmi Note 13 Rostest (EAC) 8/ 512 GB, black</t>
+          <t>Смартфон HONOR 200/ 200 Pro</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>2 197 404 UZS</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>https://uz.ozon.com/product/xiaomi-smartfon-redmi-note-13-rostest-eac-8-512-gb-chernyy-1680202980/?at=x6tPnPqN9UW43vm0CjYYVDyhwJgq6OH3qQOKqtAR3AYN</t>
+          <t>3 839 040</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-honor-200-200-pro-chernyj---1-1841703</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Original</t>
-        </is>
-      </c>
+          <t>5.0 (3 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон W&amp;O X 16 8/128 ГБ, X 15 pro max 4/64 ГБ</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>958 080</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-wo-x-16-8128-gb-tyomno-seryj---254-1487310</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>3.5 (1120 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Premier P50 8/256ГБ</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>2 591 040</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-premier-p50-8256gb-1618221</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Redmi Note 14 pro, 12GB+512GB, AMOLED 120Hz дисплей</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>3 071 040</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-redmi-note-svetlo-sinij---281-1436235</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>4.8 (72 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Tecno CAMON 40,бонус Bluetooth наушники TWS M10,50МП,120Гц,8/256ГБ,гарантия 1 год</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>3 071 040</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-tecno-camon-seryj-metallik---291-1860727</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон HONOR 400 - 120 Гц, 6000 мА/ч, 200 Мп + наушники, gift box в подарок</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>5 327 040</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-honor-400-zolotoj---133-1779227</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (4 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy S24 Ultra, 12/256 GB</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>11 774 016</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/samsung-galaxy-s24-ultra-12256-gb-chernyj---1-1735008</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (2 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Мини смартфон ONEMYTH M16 Pro</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>767 040</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/mini-smartfon-onemyth-m16-pro-chernyj---1-1758248</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>4.0 (4 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Realme C55 8+4/256GB, 90Hz, 6.72 дюймов, Android 13, 5000mah, NFC, камера 64mp</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>1 566 720</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-realme-c55-chernyj---1-1626648</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>4.0 (2 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Redmi Note 14 pro, 12GB+512GB, AMOLED 120Hz дисплей</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>4 155 840</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-redmi-note-chernyj---1-1436523</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>4.8 (463 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Infinix Smart 10, 4+4/128 ГБ</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>997 440</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-smart-10-44128-gb-serebryanyj---4-1835407</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (3 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Xiaomi Poco X7 Pro 5G, 50MP, 6000 мА/ч, NFC</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>4 568 640</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-xiaomi-poco-zheltyj---118-1468971</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>4.8 (62 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Honor 400 Lite 5G 8/256 Гб, 108 МП улучшенная камера с ИИ, AMOLED дисплей 5230мАч</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>3 234 240</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-honor-400-seryj---3-1680230</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>4.7 (19 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A06, 6+128GB, 6.7" большой дисплей, главная камера 50 MP, Dual Sim</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>1 437 120</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-chernyj---1-1581732</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (2 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Infinix smart 9, 3/128, Neo Titanium, 5000 мА/ч, MediaTek HElio G81</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>1 108 800</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-smart-chernyj---1-1640390</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (6 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy S24 Ultra 12/256 12/512 ГБ</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>12 267 840</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-s24-ultra-12256-seryj-metallik---291-1422216</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>4.9 (9 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон realme C75</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>2 112 000</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-realme-c75-chernyj---1-1779115</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (2 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Tecno Pova 6, 12/256+32ГБ, аккумулятор 6000 мАh, ультра-зарядка, AMOLED 120ГЦ</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>2 971 200</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-tecno-pova-tyomno-seryj---254-1582194</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (2 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>OPPO A5x4+128GB 45W 6000mhA IP65</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>1 892 160</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/oppo-a5x4128gb-45w-6000mha-ip65-belyj---5-1869267</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (1 отзыв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Vivo X200 FE, 12+512 ГБ, 6500 mAч батарея, 120 Гц Amoled экран</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>10 550 400</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-vivo-x200-sinij---125-1852238</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>Телефон Redmi 13C 8 ГБ 256 ГБ NFC, 5000 мач, тройной камерой 50 мп, 18wt, два слота сим</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>1 576 320</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/telefon-redmi-13c-chernyj---1-1673056</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>2.7 (14 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Vivo Y19s 6+6/128ГБ, 90 Hz, 5500 мА/ч , 50 Мп + 0,08 Мп</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>1 823 040</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-vivo-y19s-sinij-melanzh---252-1300910</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>4.7 (12 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Honor X6c, 6/256 Гб, 6.61" 120 Гц, 5300 мА/ч</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>1 622 400</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-honor-x6c-salatovyj---277-1763466</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>4.8 (4 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Tecno SPARK GO 1, бонусные Bluetooth-наушники TWS M10, 3/148, гарантия 1 год</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>1 151 040</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-tecno-spark-bezhevyj---11-1860789</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Infinix HOT 60 Pro+, 8/256 ГБ, изогнутый 3D AMOLED экран 144Гц, 50 МП, 5160 мА/ч, 45 Вт</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>2 880 000</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-hot-chernyj---1-1873143</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (1 отзыв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>IPhone Xr в 16 про корпусе</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>4 802 000</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/iphone-xr-v-16-pro-korpuse-bezhevyj---11-1772001</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Honor 400 Pro 12+512 ГБ, 5G, Snapdragon 8 Gen 3, 200 МП, AMOLED 6000 мАч +подарок</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>8 639 040</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-honor-400-chernyj---1-1785764</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (1 отзыв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Tecno SPARK 40 Pro,Бонус Bluetooth-наушники TWS M10,50МП,144Гц,5200мАч,45Вт,60ФПС</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>2 399 040</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-tecno-spark-serebryanyj---4-1865018</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон M-horse C68 8/256GB, Android, беспроводной наушник подарок, iPhone в стиле</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>1 413 120</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-mhorse-c68-zolotoj---133-1752037</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (4 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Xiaomi Redmi 15, бонусные Bluetooth-наушники TWS M10, 7000 мАч 33 Вт, 144Гц, 50МП</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>2 111 040</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-xiaomi-redmi-bezhevyj-melanzh---249-1872231</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Xiaomi Poco C71, 4+128ГБ, 32 Мп двойная камера, 6,88" дисплей</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>1 055 040</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-xiaomi-poco-chernyj---1-1797693</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>4.8 (5 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>HTC Wildfire E5 4/64 ГБ, 6.745" 90Гц, 4920 мАч, Android 14, Dual SIM</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>863 040</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/htc-wildfire-e5-chernyj---1-1826507</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>Телефон Jiaenova A16 Max!</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>1 391 040</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/telefon-jiaenova-a16-max-indigo---251-1875871</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (6 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy A35, 8/128 Гб</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>3 733 440</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/samsung-galaxy-a35-8128-gb-1863181</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy M16 5G, бонус Адаптер,экран Super AMOLED,50 Мп</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>2 159 040</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-chernyj---1-1786039</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (1 отзыв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Motorola Edge 50 Fusion 5G В подарок Bluetooth наушники TWS M10, 12/512ГБ, 50 МП, NFC</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>4 703 040</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-motorola-edge-sinij-melanzh---252-1448376</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (9 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Honor 400 Lite 5G 8/256 Гб, 108 МП улучшенная камера с ИИ, AMOLED дисплей 5230мАч</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>3 153 600</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-honor-400-seryj---3-1757896</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>4.6 (22 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон ZTE Blade A75 5G 4/128 5000mAh/ 2025</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>1 391 990</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-zte-blade-a75-5g-4128-1858160</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>Телефон Смартфон W&amp;O X 16 PRO MAX 8 ГБ/128 ГБ Чехол и защитное стекло в подарок</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>1 055 040</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/telefon-smartfon-wo-zolotoj---133-1875903</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (7 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Infinix HOT 60i, до 8+8 16/256Gb, 50 МП, 45 Вт 5160 мА·ч, Helio G81 Ultimate</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>2 015 040</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-hot-serebryanyj---4-1821533</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>Телефон Смартфон W&amp;O X 16 PRO MAX 8 ГБ/128 ГБ Чехол и защитное стекло в подарок</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>1 055 040</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/telefon-smartfon-wo-belyj---5-1875903</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (7 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A36 5G, 8GB 256GB, SAMOLED 120Hz 6.7", 5000 mAh, 50мп</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>3 984 000</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-chernyj---1-1764824</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (2 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Apple iPhone 12 Pro, 128/256 ГБ, SIM+Esim, чехол и стекло в подарок</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>7 938 000</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-apple-iphone-chernyj---1-1648466</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>4.7 (7 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A06,5000мАч,быстрая 25Вт,камера 50Мп,2 SIM-карты,гарантия 1 год</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>1 343 040</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-zolotoj---133-1305234</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (2 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy S25 Ultra 5G 12, 256, 512, чехол</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>14 303 040</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-chernyj---1-1512116</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>4.7 (3 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A56</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>4 790 400</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-a56-chernoe-steklo---1011-1798708</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (2 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон андроид 6/1024 ГБ амолед экран, 16 про макс</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>2 879 040</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-android-61024-seryj---3-1752362</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A16 8/256 ГБ, 6/128 ГБ, 2 SIM 50 Мп, SUPER AMOLED</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>1 992 960</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-belyj---5-1815928</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>4.4 (7 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>IPhone 16 Pro/Pro Max, 128/256/512/1 ТБ, DualSim+ SIM+eSIM</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>16 659 020</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/iphone-16-propro-mednyj---288-1283865</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (33 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Redmi Note 14, 8+256 Гб, AMOLED 120 Hz дисплей, 6.67"</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>2 110 080</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-redmi-note-chernyj---1-1763903</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Vivo Y29 + 2 подарка – 6.72" 120 Гц, 8+256 ГБ, 50 МП AI-камера, 6500 мАч</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>2 783 040</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-vivo-y29-belyj---5-1796556</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Honor X9C</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>4 560 000</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-honor-x9c-1580347</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Infinix HOT 60i, до 8+8 16/256Gb, 50 МП, 45 Вт 5160 мА·ч, Helio G81 Ultimate</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>1 855 680</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-hot-chernyj---1-1865570</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Infinix Hot 40 Pro, 16 / 256, 21 / 256, 108 MP+2 MP, NFC 5000 мА/ч + 32GB флеш-карта</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>2 236 800</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-hot-zolotoj---133-1460266</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>4.8 (46 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Apple iPhone XR, 128/256 ГБ</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>5 879 020</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-apple-iphone-xr-128256-gb-chernyj---1-1674582</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy S24 FE, 256 ГБ</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>7 958 400</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-s24-fe-256-svetlo-bezhevyj---255-1749559</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>Телефон, Смартфон W&amp;O X 25 ULTRA 8ГБ/128 ГБ Чехол и защитное стекло в подарок</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>1 166 400</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/telefon-smartfon-wo-prozrachnyj---234-1875929</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (3 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон TAKTEL NOTE 30 PRO VIP</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>864 000</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-taktel-note-30-pro-vip-zelenyj---120-1633555</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>3.8 (11 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Huawei Nova 11, 50MP, селфи 60MP, NFC, 120 Гц, 66 Вт быстрая зарядка</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>2 399 040</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-huawei-nova-molochnyj---257-1803524</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (4 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A06, 6+128GB, 6.7" большой дисплей, главная камера 50 MP, Dual Sim</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>1 437 120</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-ledyanoj---129-1581732</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (2 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A56 5G, 50 МП, Super AMOLED, 120 Гц</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>4 799 040</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-chernyj---1-1716010</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (3 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Infinix Smart 10, 4+4/128GB gacha, 5000mAh 15w, 6.67" 120Hz, IP 64, Android 15</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>1 104 000</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-smart-zolotoj---133-1864858</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон стиль iPhone, 16 Pro Max, 8/128 ГБ, M-HORSE 5000mah, наушники в подарок</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>3 168 000</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-stil-iphone-limonnyj---119-1822365</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>4.0 (4 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A06 4/128GB, 6/128GB, 50 МП, 2SIM, 5000 мА/ч</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>2 640 000</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-chernyj---1-1791984</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>4.2 (20 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A36</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>4 118 400</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-a36-chernoe-steklo---1011-1798742</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон iPhone XR16 Pro 64 ГБ Desert Titan dual sim</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>5 291 020</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-iphone-xr16-1593281</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>3.0 (4 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy S24 Ultra</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>19 190 400</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/samsung-galaxy-s24-ultra-chernyj---1-1710695</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A26 5G, 6.7", Super AMOLED, 120 Гц, 5000 мА/ч, 50 МП</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>3 134 400</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-chernyj---1-1815640</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>4.5 (2 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Apple iPhone 13, 128/256 ГБ</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>7 693 000</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-apple-iphone-13-128256-gb-belyj---5-1801986</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (1 отзыв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Vivo Y29 + 2 подарка – 6.72" 120 Гц, 8+256 ГБ, 50 МП AI-камера, 6500 мАч</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>2 783 040</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-vivo-y29-korichnevyj---6-1796556</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Apple iPhone 16 Pro/Pro Max, 128/256/512/1 ТБ, DualSim+ SIM+eSIM</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>15 672 160</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-apple-iphone-mednyj---288-1517432</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (3 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy M16 5G, бонус Адаптер, экран Super AMOLED, 50 Мп</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>2 275 200</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-chernyj---1-1823276</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Honor X7c, 16GB(8+8)+512GB, водонепроницаемый, сверхбольшое время работы батареи</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>2 328 000</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-honor-x7c-belyj---5-1758014</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>4.8 (4 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон W&amp;O X25 ultra 8/128 ГБ, 5200 мАч, с ручкой, стиль Samsung S25 ultra, android</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>1 267 200</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-wo-x25-chernyj---1-1753368</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>3.3 (4 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy S24 Ultra 5G, в подарок чехол</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>12 277 440</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-bezhevyj-melanzh---249-1830210</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (1 отзыв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Redmi 15C, 8/256Гб, 6000мА/ч, 6.9"дисплей, 50МП камера с ИИ, 33Вт быстрая зарядка</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>1 535 040</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-redmi-15c-chernyj---1-1864373</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (2 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy S25 12Gb+128GB/ 12Gb+256GB</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>10 063 680</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-s25-12gb128gb-12gb256gb-temno-sinij---209-1798799</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A56, 8/128 Gb, 8/256 Gb</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>4 799 040</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-a56-8128-gb-khrom---290-1848616</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Honor 400, 120Hz, 12ГБ/512ГБ, 6.55" AMOLED, 200Мп</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>4 895 040</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-honor-400-chernyj---1-1838672</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Apple iPhone 13, 128/256 ГБ, SIM+eSIM, чехол в подарок</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>7 349 020</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-apple-iphone-zelenyj---120-1121788</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (14 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Honor 400 Lite 5G 8/256GB, 108 МП улучшенная камера с ИИ, AMOLED дисплей 5230мАч</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>3 187 190</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-honor-400-chernyj---1-1818568</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (2 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон iPhone 16, 128/256 ГБ, E-SIM, чехол и стекло в подарок</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>10 966 200</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-iphone-16-belyj---5-1875870</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Redmi Note 14 Pro GLOBAL до 12/512ГБ 5500 мАч 45W AMOLED 120Hz + 1 год гарантии</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>3 504 000</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-redmi-note-chernyj---1-1764216</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (7 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Infinix HOT 50 Pro Plus, в подарок Bluetooth наушники TWS M10</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>2 975 040</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-hot-seryj-metallik---291-1340210</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Honor X9c 8/256GB, 12/256GB, 108MP, 120Hz, 6600mAh</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>4 319 040</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-honor-x9c-chernyj---1-1389332</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (7 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A26</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>3 254 400</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-a26-belyj---5-1798668</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>3.7 (3 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Xiaomi Poco X7 PRO 5G, 6000 мАч 90W, до 12/512GB, Dimensity 8400-Ultra, Face ID</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>5 567 040</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-xiaomi-poco-chernyj---1-1472780</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>4.9 (34 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>Apple iPhone 16, черный, 8/128 GB</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>11 231 780</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/apple-iphone-16-chernyj-8128-gb-belyj---5-1573266</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Apple iPhone 13 Pro Max, NFC, 5G, SIM+eSIM</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>10 779 020</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-apple-iphone-chernyj---1-1447553</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A36</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>4 118 400</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-a36-belyj---5-1798742</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A25 5G</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>3 494 400</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-a25-5g-chernyj---1-1580743</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>3.0 (2 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон HUAWEI nova 12i, гарантия 1 год,TWS M10, 108MP, NFC, Snapdragon 680</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>2 187 840</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-huawei-nova-biryuzovyj---124-1486677</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>4.0 (1 отзыв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Xiaomi Redmi Note 13 Pro+ 5G, 12/512 ГБ, 5G, камера 200 МП, NFC +Smart Watch</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>4 464 000</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-xiaomi-redmi-chernyj---1-1771492</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (8 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>IPhone 16 Pro/Pro Max, 128/256/512/1 ТБ, DualSim+ SIM+eSIM</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>16 659 020</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/iphone-16-propro-chernyj---1-1283865</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (33 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон REALME C55, 16/256ГБ, 90HZ, 5000мАч, 64МП, NFC</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>1 852 800</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-realme-c55-1643803</t>
+        </is>
+      </c>
+      <c r="D143" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung A 16</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>2 188 800</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-a-16-chernyj---1-1798630</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (2 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Redmi Note 14 Pro GLOBAL до 12/512ГБ 5500 мАч 45W AMOLED 120Hz + 1 год гарантии</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>3 504 000</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-redmi-note-fioletovyj---130-1764216</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (7 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Xiaomi Poco F7 Pro 5G, Бонус Bluetooth наушники TWS M10, Гарантия 1 год, Uzimei</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>7 487 040</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-xiaomi-poco-chernyj---1-1658202</t>
+        </is>
+      </c>
+      <c r="D146" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A36 5G, Nano + eSIM, NFC, 120 гц Super AMOLED</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>4 262 400</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-lavandovyj---132-1656554</t>
+        </is>
+      </c>
+      <c r="D147" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy S24 Ultra 5G, в подарок чехол</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>12 277 440</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-chernyj---1-1830210</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (1 отзыв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Infinix Note 50 Pro, 12+12/256 ГБ, AMOLED 144Гц, 5200 mAч 90W, беспроводная зарядка</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>3 647 040</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-note-chernyj---1-1797211</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Motorola Moto G85 5G, в подарок Bluetooth наушники TWS M10, 12/256ГБ, 50МП, 120Гц</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>3 839 040</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-motorola-moto-sinij---125-1447118</t>
+        </is>
+      </c>
+      <c r="D150" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (8 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон iPhone 16, 128/256 ГБ, LL/A, eSim, чехол и стекло в подарок</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>10 966 200</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-iphone-16-belyj---5-1776312</t>
+        </is>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон iPhone 16 Pro, Pro Max, 128, 256 ГБ, 1-SIM, Dual-SIM, стекло и чехол в подарок</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>14 690 200</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-iphone-16-bezhevyj---11-1428216</t>
+        </is>
+      </c>
+      <c r="D152" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (1 отзыв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy S25 Ultra, 12 ГБ + 256 ГБ, Dynamic AMOLED 2X 120Hz, 5000 mAh, Dual SIM</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>16 502 400</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-chernyj---1-1749531</t>
+        </is>
+      </c>
+      <c r="D153" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Redmi Note 14 Pro, 12GB+512GB, AMOLED 120Hz дисплей</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>3 744 000</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-redmi-note-chernyj---1-1709358</t>
+        </is>
+      </c>
+      <c r="D154" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (2 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A16 8/256 ГБ, 6/128 ГБ, 2 SIM 50 Мп, SUPER AMOLED</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>2 259 840</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-myatnyj---123-1815928</t>
+        </is>
+      </c>
+      <c r="D155" s="4" t="inlineStr">
+        <is>
+          <t>4.4 (7 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон M-Horse S24 Ultra, 3+5+128 ГБ</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>1 240 320</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-mhorse-s24-ultra-35128-gb-fioletovyj---130-1488938</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr">
+        <is>
+          <t>4.5 (4 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A26 5G 8/128GB, 8/256GB</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>3 219 840</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-a26-5g-8128gb-chernyj---1-1731053</t>
+        </is>
+      </c>
+      <c r="D157" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (1 отзыв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Honor 400 Pro, 200+50MP, 6000 мА/ч, IP69, 6.67", 120Hz, AMOLED, AI функции</t>
+        </is>
+      </c>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t>7 967 040</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-honor-400-seryj---3-1838706</t>
+        </is>
+      </c>
+      <c r="D158" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (1 отзыв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A55, 8+256 ГБ, 8+128 ГБ, Super AMOLED 6.6" 120 Гц</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>5 104 320</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-chernyj---1-1580804</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (1 отзыв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Apple iPhone 13, 128/256 ГБ, 1 SIM/Dual SIM</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>8 222 200</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-apple-iphone-belyj---5-1454723</t>
+        </is>
+      </c>
+      <c r="D160" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>HONOR 400 5G (Global, 8/256 GB, MagicOS 9 на Android 15)</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>4 995 840</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/honor-400-5g-svetlo-sinij---281-1801163</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (1 отзыв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A14, 50MП, 5000mAч, NFC, Uzimei зарегистрирован, гарантия 1 год</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>2 015 040</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-chernyj---1-1734224</t>
+        </is>
+      </c>
+      <c r="D162" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (3 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Xiaomi Redmi Note 13 Pro+ 5G, 12/512 ГБ, 5G, камера 200 МП, NFC +Smart Watch</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>4 464 000</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-xiaomi-redmi-belyj---5-1771492</t>
+        </is>
+      </c>
+      <c r="D163" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (8 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy a06 4/128</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>1 584 000</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-a06-4128-1562174</t>
+        </is>
+      </c>
+      <c r="D164" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A26 5G, 6.7", Super AMOLED, 120 Гц, 5000 мА/ч, 50 МП</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>3 134 400</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-myatnyj---123-1815640</t>
+        </is>
+      </c>
+      <c r="D165" s="4" t="inlineStr">
+        <is>
+          <t>4.5 (2 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy S24 FE 5G</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t>7 583 040</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-s24-fe-5g-ugolnyj---2-1268184</t>
+        </is>
+      </c>
+      <c r="D166" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (4 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A56 5G, 8GB 256GB, SAMOLED 120Hz 6.7", 5000 mAh</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>4 785 600</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-chernyj---1-1763135</t>
+        </is>
+      </c>
+      <c r="D167" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (2 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung A 16</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>2 188 800</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-a-16-lesnoj-zelenyj---121-1798630</t>
+        </is>
+      </c>
+      <c r="D168" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (2 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy S25 12GB+256GB, Dynamic AMOLED 2X 120Гц, 4000 мАч, Dual SIM</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>10 512 000</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-seryj-metallik---291-1797234</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Redmi 9A,64ГБ (32+32), 5000 мАч, 6.53" HD+ DotDrop дисплей, MediaTek Helio G25</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>1 075 200</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-redmi-9a64gb-chernyj---1-1589837</t>
+        </is>
+      </c>
+      <c r="D170" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (2 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Infinix Smart 10, 4+4/128GB gacha, 5000mAh 15w, 6.67" 120Hz, IP 64, Android 15</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>1 180 800</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-smart-chernyj---1-1829903</t>
+        </is>
+      </c>
+      <c r="D171" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (7 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Infinix HOT 60 PRO+, 8/128 ГБ, 8/256 ГБ, в разных цветах</t>
+        </is>
+      </c>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t>3 311 040</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-hot-tyomno-seryj---254-1855091</t>
+        </is>
+      </c>
+      <c r="D172" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон iPhone 16 Pro, Pro Max, 256 ГБ, 512 ГБ, 1 ТБ, E-SIM, стекло и чехол в подарок</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>14 396 200</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-iphone-16-chernyj---1-1682447</t>
+        </is>
+      </c>
+      <c r="D173" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Xiaomi Poco X7 Pro, 12GB+512GB, 6,67" AMOLED 120Hz дисплей, 6000 мА/ч, 5G</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t>4 511 040</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-xiaomi-poco-zheltyj---118-1874644</t>
+        </is>
+      </c>
+      <c r="D174" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A36 5G, 8/256 GB, Super AMOLED 120 Hz 6.7", 5000 mA/h, 50 Мп</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>4 080 000</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-chernyj---1-1762477</t>
+        </is>
+      </c>
+      <c r="D175" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (1 отзыв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон OPPO F11, 8/256 ГБ, Helio P70 (8 ядер), 2.1 ГГц, 48 МП + 5 МП, 4020 мАч</t>
+        </is>
+      </c>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t>1 180 800</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-oppo-f11-belyj---5-1606767</t>
+        </is>
+      </c>
+      <c r="D176" s="4" t="inlineStr">
+        <is>
+          <t>3.0 (6 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A56 5G,бонус адаптер,Uzimei ,1 год гаранти,50МП,Super AMOLED,120Гц</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>7 776 000</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-tyomno-seryj---254-1577696</t>
+        </is>
+      </c>
+      <c r="D177" s="4" t="inlineStr">
+        <is>
+          <t>4.8 (5 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Infinix Hot 50, 8+8/256 ГБ черный</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
+          <t>2 080 320</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-hot-50-88256-gb-1450297</t>
+        </is>
+      </c>
+      <c r="D178" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Infinix HOT 60 Pro+ 8/256 ГБ изогнутый 3D AMOLED экран 144Гц 50 МП 5160 мАч 45 Вт</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>2 952 000</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-hot-serebryanyj---4-1875105</t>
+        </is>
+      </c>
+      <c r="D179" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy F16 5G,экран Super AMOLED, камера 50 МП, 5000 мА/ч, гарантия 1 год</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>2 207 040</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-ugolnyj---2-1745184</t>
+        </is>
+      </c>
+      <c r="D180" s="4" t="inlineStr">
+        <is>
+          <t>4.5 (2 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A56</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>4 790 400</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-a56-serebryanyj---4-1798708</t>
+        </is>
+      </c>
+      <c r="D181" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (2 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A26 5G, Uzimei, 1 год гарантии, 50 МП, 5000 мА/ч, 120 Гц</t>
+        </is>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>3 435 840</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-chernyj---1-1642866</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Infinix NOTE 50, 50 МП камера OIS, 8+8/ 256 ГБ, 5200 мАч, 45W+30W быстр заряд, 144Гц AMOLED</t>
+        </is>
+      </c>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t>3 167 040</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-note-bezhevyj---11-1803467</t>
+        </is>
+      </c>
+      <c r="D183" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Honor 400 5G,бонус Honor choice наушники и GIFT box, 200МП,6000мАч 66Вт,120Гц,</t>
+        </is>
+      </c>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
+          <t>5 355 840</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-honor-400-bezhevyj---11-1774505</t>
+        </is>
+      </c>
+      <c r="D184" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (2 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон HUAWEI nova Y73,бонусные Bluetooth-наушники TWS M10,50МП,NFC, аккумулятор 6620мАч</t>
+        </is>
+      </c>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>2 034 240</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-huawei-nova-chernyj---1-1761630</t>
+        </is>
+      </c>
+      <c r="D185" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (2 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Redmi A5, 3/64 ГБ, 4/128 ГБ, 120 Hz, 6.88", 5200 mAh</t>
+        </is>
+      </c>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>1 038 720</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-redmi-a5-bezhevyj---11-1797556</t>
+        </is>
+      </c>
+      <c r="D186" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Redmi Note 14, 8 GB+256 GB, AMOLED 120Hz дисплей, 6.67"</t>
+        </is>
+      </c>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>2 378 880</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-redmi-note-chernyj---1-1787112</t>
+        </is>
+      </c>
+      <c r="D187" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (2 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A16 8+256ГБ, Super AMOLED, 90Hz 6.7", 50 MP</t>
+        </is>
+      </c>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t>2 207 040</t>
+        </is>
+      </c>
+      <c r="C188" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-zelenyj---120-1760468</t>
+        </is>
+      </c>
+      <c r="D188" s="4" t="inlineStr">
+        <is>
+          <t>4.5 (11 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="inlineStr">
+        <is>
+          <t>Флагман больше не мечта — W&amp;O A56 создан для вас!</t>
+        </is>
+      </c>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>1 247 040</t>
+        </is>
+      </c>
+      <c r="C189" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/flagman-bolshe-ne-mechta-wo-a56-rozovyj---16-1823685</t>
+        </is>
+      </c>
+      <c r="D189" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="inlineStr">
+        <is>
+          <t>IPhone 16 pro max</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>19 590 200</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/iphone-16-pro-max-pudrovyj---287-1662752</t>
+        </is>
+      </c>
+      <c r="D190" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (16 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A56 5G, 50 МП, Super AMOLED, 120 Гц</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>4 799 040</t>
+        </is>
+      </c>
+      <c r="C191" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-prozrachnyj---234-1716010</t>
+        </is>
+      </c>
+      <c r="D191" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (3 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Xiaomi Redmi Note 13 Pro+ 5G, 12/512 ГБ, 5G, камера 200 МП, NFC +Smart Watch</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>4 464 000</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-xiaomi-redmi-lavandovyj---132-1771492</t>
+        </is>
+      </c>
+      <c r="D192" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (8 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Honor 400 Lite 5G 8/256 Гб, 108 МП улучшенная камера с ИИ, AMOLED дисплей 5230мАч</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>3 153 600</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-honor-400-chernyj---1-1757896</t>
+        </is>
+      </c>
+      <c r="D193" s="4" t="inlineStr">
+        <is>
+          <t>4.6 (22 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="inlineStr">
+        <is>
+          <t>Samsung Galaxy A35, 8/128 Гб</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>3 733 440</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/samsung-galaxy-a35-8128-gb-1863181</t>
+        </is>
+      </c>
+      <c r="D194" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A26</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>3 254 400</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-a26-chernyj---1-1798668</t>
+        </is>
+      </c>
+      <c r="D195" s="4" t="inlineStr">
+        <is>
+          <t>3.7 (3 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон HUAWEI nova Y63, 6000 мАч, 50 МП, NFC</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>1 627 200</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-huawei-nova-y63-6000-mach-chernyj---1-1776574</t>
+        </is>
+      </c>
+      <c r="D196" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Honor 400 Lite 5G 8/256 Гб, 108 МП улучшенная камера с ИИ, AMOLED дисплей 5230мАч</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>3 153 600</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-honor-400-seryj---3-1757896</t>
+        </is>
+      </c>
+      <c r="D197" s="4" t="inlineStr">
+        <is>
+          <t>4.6 (22 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="inlineStr">
+        <is>
+          <t>Cмартфон HUAWEI nova Y72S, 6000 мАч, 50МП, NFC, гарантия 1 год</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>1 900 800</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/cmartfon-huawei-nova-chernyj---1-1553192</t>
+        </is>
+      </c>
+      <c r="D198" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (3 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон W&amp;O X 300 4/64 GB Android, чехол и защитное стекло в подарок</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>853 440</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-wo-x-belyj---5-1798375</t>
+        </is>
+      </c>
+      <c r="D199" s="4" t="inlineStr">
+        <is>
+          <t>4.2 (5 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон iPhone 16, 128/256 ГБ, E-SIM, чехол и стекло в подарок</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t>10 966 200</t>
+        </is>
+      </c>
+      <c r="C200" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-iphone-16-chernyj---1-1875870</t>
+        </is>
+      </c>
+      <c r="D200" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A16 8/256 ГБ, 6/128 ГБ, 2 SIM 50 Мп, SUPER AMOLED</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>1 992 960</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-temno-sinij---209-1815928</t>
+        </is>
+      </c>
+      <c r="D201" s="4" t="inlineStr">
+        <is>
+          <t>4.4 (7 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон M-HORSE Pro Max с 6/128 ГБ</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>1 506 240</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-mhorse-pro-max-s-6128-seryj-metallik---291-1632156</t>
+        </is>
+      </c>
+      <c r="D202" s="4" t="inlineStr">
+        <is>
+          <t>4.0 (4 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A36 5G, 8GB 256GB, SAMOLED 120Hz 6.7", 5000 mAh, 50мп</t>
+        </is>
+      </c>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t>3 984 000</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-chernyj---1-1764824</t>
+        </is>
+      </c>
+      <c r="D203" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (2 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Apple iPhone 12 Pro, 128/256 ГБ, SIM+Esim, чехол и стекло в подарок</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>7 938 000</t>
+        </is>
+      </c>
+      <c r="C204" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-apple-iphone-chernyj---1-1648466</t>
+        </is>
+      </c>
+      <c r="D204" s="4" t="inlineStr">
+        <is>
+          <t>4.7 (7 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy S25 Ultra 5G 12, 256, 512, чехол</t>
+        </is>
+      </c>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
+          <t>14 303 040</t>
+        </is>
+      </c>
+      <c r="C205" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-chernyj---1-1512116</t>
+        </is>
+      </c>
+      <c r="D205" s="4" t="inlineStr">
+        <is>
+          <t>4.7 (3 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Honor X7b, 8 / 128 ГБ, зеленый</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t>2 294 400</t>
+        </is>
+      </c>
+      <c r="C206" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-honor-x7b-8-128-gb-serebryanyj---4-1533643</t>
+        </is>
+      </c>
+      <c r="D206" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Honor X9C 5G, 12GB 256GB, 6.78" AMOLED, 108 + 2 Мп, NFC, быстрая зарядка 66 Вт</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
+          <t>4 159 680</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-honor-x9c-chernyj---1-1660032</t>
+        </is>
+      </c>
+      <c r="D207" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Honor 400 Pro 12+512 ГБ, 5G, Snapdragon 8 Gen 3, 200 МП, AMOLED 6000 мАч +подарок</t>
+        </is>
+      </c>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>8 639 040</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-honor-400-seryj-metallik---291-1785764</t>
+        </is>
+      </c>
+      <c r="D208" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (1 отзыв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон андроид 6/1024 ГБ амолед экран, 16 про макс</t>
+        </is>
+      </c>
+      <c r="B209" s="4" t="inlineStr">
+        <is>
+          <t>2 879 040</t>
+        </is>
+      </c>
+      <c r="C209" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-android-61024-seryj---3-1752362</t>
+        </is>
+      </c>
+      <c r="D209" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A16 8/256 ГБ, 6/128 ГБ, 2 SIM 50 Мп, SUPER AMOLED</t>
+        </is>
+      </c>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t>1 992 000</t>
+        </is>
+      </c>
+      <c r="C210" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-myatnyj---123-1839281</t>
+        </is>
+      </c>
+      <c r="D210" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A16 8/256 ГБ, 6/128 ГБ, 2 SIM 50 Мп, SUPER AMOLED</t>
+        </is>
+      </c>
+      <c r="B211" s="4" t="inlineStr">
+        <is>
+          <t>1 992 960</t>
+        </is>
+      </c>
+      <c r="C211" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-belyj---5-1815928</t>
+        </is>
+      </c>
+      <c r="D211" s="4" t="inlineStr">
+        <is>
+          <t>4.4 (7 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="4" t="inlineStr">
+        <is>
+          <t>IPhone 16 Pro/Pro Max, 128/256/512/1 ТБ, DualSim+ SIM+eSIM</t>
+        </is>
+      </c>
+      <c r="B212" s="4" t="inlineStr">
+        <is>
+          <t>16 659 020</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/iphone-16-propro-mednyj---288-1283865</t>
+        </is>
+      </c>
+      <c r="D212" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (33 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Tecno Spark 30 Pro, камера 108 MP, AMOLED, 120 Герц, 6.78 дюйма</t>
+        </is>
+      </c>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>2 226 240</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-tecno-spark-chernyj---1-1588952</t>
+        </is>
+      </c>
+      <c r="D213" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Redmi Note 14, 8+256 Гб, AMOLED 120 Hz дисплей, 6.67"</t>
+        </is>
+      </c>
+      <c r="B214" s="4" t="inlineStr">
+        <is>
+          <t>2 110 080</t>
+        </is>
+      </c>
+      <c r="C214" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-redmi-note-chernyj---1-1763903</t>
+        </is>
+      </c>
+      <c r="D214" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Infinix HOT 60i, до 8+8 16/256Gb, 50 МП, 45 Вт 5160 мА·ч, Helio G81 Ultimate</t>
+        </is>
+      </c>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t>1 855 680</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-hot-chernyj---1-1865570</t>
+        </is>
+      </c>
+      <c r="D215" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Infinix Hot 40 Pro, 16 / 256, 21 / 256, 108 MP+2 MP, NFC 5000 мА/ч + 32GB флеш-карта</t>
+        </is>
+      </c>
+      <c r="B216" s="4" t="inlineStr">
+        <is>
+          <t>2 236 800</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-hot-zolotoj---133-1460266</t>
+        </is>
+      </c>
+      <c r="D216" s="4" t="inlineStr">
+        <is>
+          <t>4.8 (46 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Honor X8c 8/256ГБ, 6.7", AMOLED, 108 МП, 5000 мАч</t>
+        </is>
+      </c>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
+          <t>2 494 080</t>
+        </is>
+      </c>
+      <c r="C217" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-honor-x8c-chernyj---1-1756591</t>
+        </is>
+      </c>
+      <c r="D217" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Apple iPhone XR, 128/256 ГБ</t>
+        </is>
+      </c>
+      <c r="B218" s="4" t="inlineStr">
+        <is>
+          <t>5 879 020</t>
+        </is>
+      </c>
+      <c r="C218" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-apple-iphone-xr-128256-gb-chernyj---1-1674582</t>
+        </is>
+      </c>
+      <c r="D218" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy S24 FE, 256 ГБ</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t>7 958 400</t>
+        </is>
+      </c>
+      <c r="C219" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-s24-fe-256-svetlo-bezhevyj---255-1749559</t>
+        </is>
+      </c>
+      <c r="D219" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон TAKTEL NOTE 30 PRO VIP</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
+        <is>
+          <t>864 000</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-taktel-note-30-pro-vip-zelenyj---120-1633555</t>
+        </is>
+      </c>
+      <c r="D220" s="4" t="inlineStr">
+        <is>
+          <t>3.8 (11 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Huawei Nova 11, 50MP, селфи 60MP, NFC, 120 Гц, 66 Вт быстрая зарядка</t>
+        </is>
+      </c>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t>2 399 040</t>
+        </is>
+      </c>
+      <c r="C221" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-huawei-nova-molochnyj---257-1803524</t>
+        </is>
+      </c>
+      <c r="D221" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (4 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон стиль iPhone, 16 Pro Max, 8/128 ГБ, M-HORSE 5000mah, наушники в подарок</t>
+        </is>
+      </c>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>3 168 000</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-stil-iphone-limonnyj---119-1822365</t>
+        </is>
+      </c>
+      <c r="D222" s="4" t="inlineStr">
+        <is>
+          <t>4.0 (4 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Honor 400, 12 ГБ / 512 ГБ, 6.55" AMOLED, 200Мп, наушники Honor в подарок</t>
+        </is>
+      </c>
+      <c r="B223" s="4" t="inlineStr">
+        <is>
+          <t>5 114 880</t>
+        </is>
+      </c>
+      <c r="C223" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-honor-400-chernyj---1-1803456</t>
+        </is>
+      </c>
+      <c r="D223" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (3 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="inlineStr">
+        <is>
+          <t>Apple iPhone 15</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
+          <t>10 141 040</t>
+        </is>
+      </c>
+      <c r="C224" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/apple-iphone-15-rozovyj---16-1710790</t>
+        </is>
+      </c>
+      <c r="D224" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A36</t>
+        </is>
+      </c>
+      <c r="B225" s="4" t="inlineStr">
+        <is>
+          <t>4 118 400</t>
+        </is>
+      </c>
+      <c r="C225" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-a36-chernoe-steklo---1011-1798742</t>
+        </is>
+      </c>
+      <c r="D225" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="4" t="inlineStr">
+        <is>
+          <t>Мини смартфон ONEMYTH M16 Pro</t>
+        </is>
+      </c>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t>767 040</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/mini-smartfon-onemyth-m16-pro-seryj---3-1758248</t>
+        </is>
+      </c>
+      <c r="D226" s="4" t="inlineStr">
+        <is>
+          <t>4.0 (4 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Apple iPhone 13, 128/256 ГБ</t>
+        </is>
+      </c>
+      <c r="B227" s="4" t="inlineStr">
+        <is>
+          <t>7 693 000</t>
+        </is>
+      </c>
+      <c r="C227" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-apple-iphone-13-128256-gb-belyj---5-1801986</t>
+        </is>
+      </c>
+      <c r="D227" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (1 отзыв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Apple iPhone 16 Pro/Pro Max, 128/256/512/1 ТБ, DualSim+ SIM+eSIM</t>
+        </is>
+      </c>
+      <c r="B228" s="4" t="inlineStr">
+        <is>
+          <t>15 672 160</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-apple-iphone-mednyj---288-1517432</t>
+        </is>
+      </c>
+      <c r="D228" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (3 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy M16 5G, бонус Адаптер, экран Super AMOLED, 50 Мп</t>
+        </is>
+      </c>
+      <c r="B229" s="4" t="inlineStr">
+        <is>
+          <t>2 275 200</t>
+        </is>
+      </c>
+      <c r="C229" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-chernyj---1-1823276</t>
+        </is>
+      </c>
+      <c r="D229" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Honor X7c, 16GB(8+8)+512GB, водонепроницаемый, сверхбольшое время работы батареи</t>
+        </is>
+      </c>
+      <c r="B230" s="4" t="inlineStr">
+        <is>
+          <t>2 328 000</t>
+        </is>
+      </c>
+      <c r="C230" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-honor-x7c-belyj---5-1758014</t>
+        </is>
+      </c>
+      <c r="D230" s="4" t="inlineStr">
+        <is>
+          <t>4.8 (4 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Xiaomi Poco C71,5200мАч, быстрая заряд 15Вт, камера 32 МП</t>
+        </is>
+      </c>
+      <c r="B231" s="4" t="inlineStr">
+        <is>
+          <t>1 247 040</t>
+        </is>
+      </c>
+      <c r="C231" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-xiaomi-poco-chernyj---1-1758742</t>
+        </is>
+      </c>
+      <c r="D231" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (1 отзыв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Xiaomi Poco C75 120Гц дисплей, 50 МП основная камера, 5160 мА/ч</t>
+        </is>
+      </c>
+      <c r="B232" s="4" t="inlineStr">
+        <is>
+          <t>1 920 000</t>
+        </is>
+      </c>
+      <c r="C232" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-xiaomi-poco-chernyj---1-1485748</t>
+        </is>
+      </c>
+      <c r="D232" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy S25 12Gb+128GB/ 12Gb+256GB</t>
+        </is>
+      </c>
+      <c r="B233" s="4" t="inlineStr">
+        <is>
+          <t>10 063 680</t>
+        </is>
+      </c>
+      <c r="C233" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-s25-12gb128gb-12gb256gb-temno-sinij---209-1798799</t>
+        </is>
+      </c>
+      <c r="D233" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Infinix Hot 50i, 6 / 128 ГБ, 4 / 256 ГБ, 5000 мА/ч, 120 Гц</t>
+        </is>
+      </c>
+      <c r="B234" s="4" t="inlineStr">
+        <is>
+          <t>1 488 960</t>
+        </is>
+      </c>
+      <c r="C234" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-hot-1682254</t>
+        </is>
+      </c>
+      <c r="D234" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (1 отзыв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A56, 8/128 Gb, 8/256 Gb</t>
+        </is>
+      </c>
+      <c r="B235" s="4" t="inlineStr">
+        <is>
+          <t>4 799 040</t>
+        </is>
+      </c>
+      <c r="C235" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-a56-8128-gb-khrom---290-1848616</t>
+        </is>
+      </c>
+      <c r="D235" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Honor X6c, 6/256 Гб, 6.61" 120 Гц, 5300 мА/ч</t>
+        </is>
+      </c>
+      <c r="B236" s="4" t="inlineStr">
+        <is>
+          <t>1 622 400</t>
+        </is>
+      </c>
+      <c r="C236" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-honor-x6c-chernyj---1-1763466</t>
+        </is>
+      </c>
+      <c r="D236" s="4" t="inlineStr">
+        <is>
+          <t>4.8 (4 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Xiaomi Poco X7 PRO 5G, 6000 мАч 90W, до 12/512GB, Dimensity 8400-Ultra, Face ID</t>
+        </is>
+      </c>
+      <c r="B237" s="4" t="inlineStr">
+        <is>
+          <t>4 555 200</t>
+        </is>
+      </c>
+      <c r="C237" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-xiaomi-poco-zheltyj---118-1472780</t>
+        </is>
+      </c>
+      <c r="D237" s="4" t="inlineStr">
+        <is>
+          <t>4.9 (34 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Infinix Smart 10, 4+4/128GB gacha, 5000mAh 15w, 6.67" 120Hz, IP 64, Android 15</t>
+        </is>
+      </c>
+      <c r="B238" s="4" t="inlineStr">
+        <is>
+          <t>1 180 800</t>
+        </is>
+      </c>
+      <c r="C238" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-smart-zolotoj---133-1829903</t>
+        </is>
+      </c>
+      <c r="D238" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (7 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Apple iPhone 13, 128/256 ГБ, SIM+eSIM, чехол в подарок</t>
+        </is>
+      </c>
+      <c r="B239" s="4" t="inlineStr">
+        <is>
+          <t>7 349 020</t>
+        </is>
+      </c>
+      <c r="C239" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-apple-iphone-zelenyj---120-1121788</t>
+        </is>
+      </c>
+      <c r="D239" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (14 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон iPhone 16 Pro, 128, 256, 512 ГБ, 1 ТБ, 1 SIM, Dual SIM, чехол в подарок</t>
+        </is>
+      </c>
+      <c r="B240" s="4" t="inlineStr">
+        <is>
+          <t>14 690 200</t>
+        </is>
+      </c>
+      <c r="C240" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-iphone-16-bezhevyj---11-1875750</t>
+        </is>
+      </c>
+      <c r="D240" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Vivo V50 Lite 8/256, 120 Hz Amoled экран</t>
+        </is>
+      </c>
+      <c r="B241" s="4" t="inlineStr">
+        <is>
+          <t>3 743 040</t>
+        </is>
+      </c>
+      <c r="C241" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-vivo-v50-lite-8256-120-chernyj---1-1651665</t>
+        </is>
+      </c>
+      <c r="D241" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (1 отзыв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="4" t="inlineStr">
+        <is>
+          <t>IPhone 16 pro max 256 gb</t>
+        </is>
+      </c>
+      <c r="B242" s="4" t="inlineStr">
+        <is>
+          <t>17 199 000</t>
+        </is>
+      </c>
+      <c r="C242" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/iphone-16-pro-max-256-gb-chernyj---1-1700293</t>
+        </is>
+      </c>
+      <c r="D242" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Infinix HOT 50 Pro Plus, в подарок Bluetooth наушники TWS M10</t>
+        </is>
+      </c>
+      <c r="B243" s="4" t="inlineStr">
+        <is>
+          <t>2 975 040</t>
+        </is>
+      </c>
+      <c r="C243" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-hot-seryj-metallik---291-1340210</t>
+        </is>
+      </c>
+      <c r="D243" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Honor X9c 8/256GB, 12/256GB, 108MP, 120Hz, 6600mAh</t>
+        </is>
+      </c>
+      <c r="B244" s="4" t="inlineStr">
+        <is>
+          <t>4 319 040</t>
+        </is>
+      </c>
+      <c r="C244" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-honor-x9c-chernyj---1-1389332</t>
+        </is>
+      </c>
+      <c r="D244" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (7 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Xiaomi Poco X7 PRO 5G, 6000 мАч 90W, до 12/512GB, Dimensity 8400-Ultra, Face ID</t>
+        </is>
+      </c>
+      <c r="B245" s="4" t="inlineStr">
+        <is>
+          <t>5 567 040</t>
+        </is>
+      </c>
+      <c r="C245" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-xiaomi-poco-chernyj---1-1472780</t>
+        </is>
+      </c>
+      <c r="D245" s="4" t="inlineStr">
+        <is>
+          <t>4.9 (34 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Apple iPhone 14 Pro/Pro Max, SIM+eSIM, NFC, 5G, чехол в подарок</t>
+        </is>
+      </c>
+      <c r="B246" s="4" t="inlineStr">
+        <is>
+          <t>13 719 020</t>
+        </is>
+      </c>
+      <c r="C246" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-apple-iphone-zolotoj---133-1284800</t>
+        </is>
+      </c>
+      <c r="D246" s="4" t="inlineStr">
+        <is>
+          <t>4.0 (4 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A36</t>
+        </is>
+      </c>
+      <c r="B247" s="4" t="inlineStr">
+        <is>
+          <t>4 118 400</t>
+        </is>
+      </c>
+      <c r="C247" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-a36-belyj---5-1798742</t>
+        </is>
+      </c>
+      <c r="D247" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Tecno Spark Go 2024 Global 4/64/128 GB, 5000mAh, 2SIM, 13+8MP</t>
+        </is>
+      </c>
+      <c r="B248" s="4" t="inlineStr">
+        <is>
+          <t>1 300 800</t>
+        </is>
+      </c>
+      <c r="C248" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-tecno-spark-chernyj---1-1668041</t>
+        </is>
+      </c>
+      <c r="D248" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон HUAWEI nova 12i, гарантия 1 год,TWS M10, 108MP, NFC, Snapdragon 680</t>
+        </is>
+      </c>
+      <c r="B249" s="4" t="inlineStr">
+        <is>
+          <t>2 187 840</t>
+        </is>
+      </c>
+      <c r="C249" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-huawei-nova-biryuzovyj---124-1486677</t>
+        </is>
+      </c>
+      <c r="D249" s="4" t="inlineStr">
+        <is>
+          <t>4.0 (1 отзыв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Xiaomi Redmi 14C, 8+256Гб, 5160 мА/ч батарея, быстрая зарядка 18W камера 50 МП AI</t>
+        </is>
+      </c>
+      <c r="B250" s="4" t="inlineStr">
+        <is>
+          <t>1 705 920</t>
+        </is>
+      </c>
+      <c r="C250" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-xiaomi-redmi-chernyj---1-1631076</t>
+        </is>
+      </c>
+      <c r="D250" s="4" t="inlineStr">
+        <is>
+          <t>4.5 (44 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="4" t="inlineStr">
+        <is>
+          <t>IPhone 16 Pro/Pro Max, 128/256/512/1 ТБ, DualSim+ SIM+eSIM</t>
+        </is>
+      </c>
+      <c r="B251" s="4" t="inlineStr">
+        <is>
+          <t>16 659 020</t>
+        </is>
+      </c>
+      <c r="C251" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/iphone-16-propro-chernyj---1-1283865</t>
+        </is>
+      </c>
+      <c r="D251" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (33 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон W&amp;O, 4/64 ГБ, в подарок чехол и защитная плёнка</t>
+        </is>
+      </c>
+      <c r="B252" s="4" t="inlineStr">
+        <is>
+          <t>863 040</t>
+        </is>
+      </c>
+      <c r="C252" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-wo-464-goluboj---127-1799663</t>
+        </is>
+      </c>
+      <c r="D252" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (3 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A16 8/256 ГБ, 6/128 ГБ, 2 SIM 50 Мп, SUPER AMOLED</t>
+        </is>
+      </c>
+      <c r="B253" s="4" t="inlineStr">
+        <is>
+          <t>2 123 520</t>
+        </is>
+      </c>
+      <c r="C253" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-myatnyj---123-1377834</t>
+        </is>
+      </c>
+      <c r="D253" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (15 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон 25 ultra 8/128 ГБ, 5200 мАч, с ручкой, стиль Samsung S25 ultra, android</t>
+        </is>
+      </c>
+      <c r="B254" s="4" t="inlineStr">
+        <is>
+          <t>1 240 320</t>
+        </is>
+      </c>
+      <c r="C254" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-25-ultra-tyomno-seryj---254-1750634</t>
+        </is>
+      </c>
+      <c r="D254" s="4" t="inlineStr">
+        <is>
+          <t>3.4 (5 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="4" t="inlineStr">
+        <is>
+          <t>Флагман больше не мечта — W&amp;O A56 создан для вас!</t>
+        </is>
+      </c>
+      <c r="B255" s="4" t="inlineStr">
+        <is>
+          <t>1 247 040</t>
+        </is>
+      </c>
+      <c r="C255" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/flagman-bolshe-ne-mechta-wo-a56-indigo---251-1823685</t>
+        </is>
+      </c>
+      <c r="D255" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Horse 25 ultra 8/128 ГБ, 5000 мАч, с ручкой, стиль Samsung S25 ultra, android</t>
+        </is>
+      </c>
+      <c r="B256" s="4" t="inlineStr">
+        <is>
+          <t>1 269 120</t>
+        </is>
+      </c>
+      <c r="C256" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-horse-25-zolotoj---133-1867351</t>
+        </is>
+      </c>
+      <c r="D256" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung A 16</t>
+        </is>
+      </c>
+      <c r="B257" s="4" t="inlineStr">
+        <is>
+          <t>2 188 800</t>
+        </is>
+      </c>
+      <c r="C257" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-a-16-chernyj---1-1798630</t>
+        </is>
+      </c>
+      <c r="D257" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (2 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="4" t="inlineStr">
+        <is>
+          <t>Планшет Honor Pad X9 11,5" LTE 4/128ГБ</t>
+        </is>
+      </c>
+      <c r="B258" s="4" t="inlineStr">
+        <is>
+          <t>3 168 000</t>
+        </is>
+      </c>
+      <c r="C258" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/planshet-honor-pad-x9-115-lte-1801186</t>
+        </is>
+      </c>
+      <c r="D258" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Xiaomi Redmi 13C, 4/28 ГБ, 8/256 ГБ, 6.74" 90 Гц, 5000 мА/ч, 4G LTE</t>
+        </is>
+      </c>
+      <c r="B259" s="4" t="inlineStr">
+        <is>
+          <t>1 463 040</t>
+        </is>
+      </c>
+      <c r="C259" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-xiaomi-redmi-1287060</t>
+        </is>
+      </c>
+      <c r="D259" s="4" t="inlineStr">
+        <is>
+          <t>3.6 (48 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy M16 5G, бонус Адаптер,экран Super AMOLED,50 Мп</t>
+        </is>
+      </c>
+      <c r="B260" s="4" t="inlineStr">
+        <is>
+          <t>2 159 040</t>
+        </is>
+      </c>
+      <c r="C260" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-pudrovyj---287-1786039</t>
+        </is>
+      </c>
+      <c r="D260" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (1 отзыв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Xiaomi Poco F7 Pro 5G, Бонус Bluetooth наушники TWS M10, Гарантия 1 год, Uzimei</t>
+        </is>
+      </c>
+      <c r="B261" s="4" t="inlineStr">
+        <is>
+          <t>7 487 040</t>
+        </is>
+      </c>
+      <c r="C261" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-xiaomi-poco-chernyj---1-1658202</t>
+        </is>
+      </c>
+      <c r="D261" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Tecno Spark Go 2024 2/64 Гб, 8/128 Гб, 16/256 Гб, DTS, 2SIM, NFC</t>
+        </is>
+      </c>
+      <c r="B262" s="4" t="inlineStr">
+        <is>
+          <t>1 167 360</t>
+        </is>
+      </c>
+      <c r="C262" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-tecno-spark-belyj---5-1692596</t>
+        </is>
+      </c>
+      <c r="D262" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A36 5G, Nano + eSIM, NFC, 120 гц Super AMOLED</t>
+        </is>
+      </c>
+      <c r="B263" s="4" t="inlineStr">
+        <is>
+          <t>4 262 400</t>
+        </is>
+      </c>
+      <c r="C263" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-lavandovyj---132-1656554</t>
+        </is>
+      </c>
+      <c r="D263" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Apple iPhone XR, 128/256 ГБ</t>
+        </is>
+      </c>
+      <c r="B264" s="4" t="inlineStr">
+        <is>
+          <t>5 879 020</t>
+        </is>
+      </c>
+      <c r="C264" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-apple-iphone-xr-128256-gb-chernyj---1-1670395</t>
+        </is>
+      </c>
+      <c r="D264" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (3 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Infinix Note 50 Pro, 12+12/256 ГБ, AMOLED 144Гц, 5200 mAч 90W, беспроводная зарядка</t>
+        </is>
+      </c>
+      <c r="B265" s="4" t="inlineStr">
+        <is>
+          <t>3 647 040</t>
+        </is>
+      </c>
+      <c r="C265" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-note-chernyj---1-1797211</t>
+        </is>
+      </c>
+      <c r="D265" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Infinix Note 50 Pro, 12+12/256 ГБ, AMOLED 144Гц, 5200 mAч 90W, беспроводная зарядка</t>
+        </is>
+      </c>
+      <c r="B266" s="4" t="inlineStr">
+        <is>
+          <t>3 647 040</t>
+        </is>
+      </c>
+      <c r="C266" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-note-tyomno-rozovyj---284-1797211</t>
+        </is>
+      </c>
+      <c r="D266" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Xiaomi Poco X7 PRO 5G, 6000 мА/ч 90W, до 12/512 ГБ, Dimensity 8400-Ultra, Face ID</t>
+        </is>
+      </c>
+      <c r="B267" s="4" t="inlineStr">
+        <is>
+          <t>4 790 400</t>
+        </is>
+      </c>
+      <c r="C267" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-xiaomi-poco-1727472</t>
+        </is>
+      </c>
+      <c r="D267" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Xiaomi Poco F7 Ultra 5G, Snapdragon 8 Elite, AMOLED 120 Гц, 5300 мАч 120Вт</t>
+        </is>
+      </c>
+      <c r="B268" s="4" t="inlineStr">
+        <is>
+          <t>10 742 400</t>
+        </is>
+      </c>
+      <c r="C268" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-xiaomi-poco-chernyj---1-1656801</t>
+        </is>
+      </c>
+      <c r="D268" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Infinix Hot 40 Pro, 16 / 256, 21 / 256, 108 MP+2 MP, NFC 5000 мА/ч</t>
+        </is>
+      </c>
+      <c r="B269" s="4" t="inlineStr">
+        <is>
+          <t>2 260 800</t>
+        </is>
+      </c>
+      <c r="C269" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-hot-chernyj---1-1480299</t>
+        </is>
+      </c>
+      <c r="D269" s="4" t="inlineStr">
+        <is>
+          <t>4.6 (7 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Motorola Moto G85 5G, в подарок Bluetooth наушники TWS M10, 12/256ГБ, 50МП, 120Гц</t>
+        </is>
+      </c>
+      <c r="B270" s="4" t="inlineStr">
+        <is>
+          <t>3 839 040</t>
+        </is>
+      </c>
+      <c r="C270" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-motorola-moto-sinij---125-1447118</t>
+        </is>
+      </c>
+      <c r="D270" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (8 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="4" t="inlineStr">
+        <is>
+          <t>W&amp;O X 100 смартфон W&amp;O, 4/64 ГБ, в подарок чехол и защитная плёнка</t>
+        </is>
+      </c>
+      <c r="B271" s="4" t="inlineStr">
+        <is>
+          <t>863 040</t>
+        </is>
+      </c>
+      <c r="C271" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/wo-x-100-indigo---251-1871919</t>
+        </is>
+      </c>
+      <c r="D271" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A16 8/256 ГБ, 6/128 ГБ, 2 SIM 50 Мп, SUPER AMOLED</t>
+        </is>
+      </c>
+      <c r="B272" s="4" t="inlineStr">
+        <is>
+          <t>1 992 000</t>
+        </is>
+      </c>
+      <c r="C272" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-chernyj---1-1839281</t>
+        </is>
+      </c>
+      <c r="D272" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон iPhone 16 Pro, Pro Max, 128, 256 ГБ, 1-SIM, Dual-SIM, стекло и чехол в подарок</t>
+        </is>
+      </c>
+      <c r="B273" s="4" t="inlineStr">
+        <is>
+          <t>14 690 200</t>
+        </is>
+      </c>
+      <c r="C273" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-iphone-16-bezhevyj---11-1428216</t>
+        </is>
+      </c>
+      <c r="D273" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (1 отзыв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy S24 5G, в подарок чехол,Гарантия 1 год, 256/128 ГБ</t>
+        </is>
+      </c>
+      <c r="B274" s="4" t="inlineStr">
+        <is>
+          <t>8 447 040</t>
+        </is>
+      </c>
+      <c r="C274" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-chernyj---1-1284857</t>
+        </is>
+      </c>
+      <c r="D274" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (1 отзыв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A36 5G, 8GB 256GB, SAMOLED 120Hz 6.7", 5000 mAh, 50мп</t>
+        </is>
+      </c>
+      <c r="B275" s="4" t="inlineStr">
+        <is>
+          <t>3 984 000</t>
+        </is>
+      </c>
+      <c r="C275" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-lavandovyj---132-1764824</t>
+        </is>
+      </c>
+      <c r="D275" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (2 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Xiaomi Redmi Note 13, 8/128, 8/256, 6.67", 120 Гц</t>
+        </is>
+      </c>
+      <c r="B276" s="4" t="inlineStr">
+        <is>
+          <t>2 496 000</t>
+        </is>
+      </c>
+      <c r="C276" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-xiaomi-redmi-chernyj---1-1287038</t>
+        </is>
+      </c>
+      <c r="D276" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (6 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A26 5G 8/128GB, 8/256GB</t>
+        </is>
+      </c>
+      <c r="B277" s="4" t="inlineStr">
+        <is>
+          <t>3 219 840</t>
+        </is>
+      </c>
+      <c r="C277" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-a26-5g-8128gb-chernyj---1-1731053</t>
+        </is>
+      </c>
+      <c r="D277" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (1 отзыв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Infinix HOT 50 Pro+ 8/256ГБ Изогнутый 3D AMOLED экран 120 Гц 50 МП 5000 мАч 33 Вт</t>
+        </is>
+      </c>
+      <c r="B278" s="4" t="inlineStr">
+        <is>
+          <t>2 880 000</t>
+        </is>
+      </c>
+      <c r="C278" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-infinix-hot-1837601</t>
+        </is>
+      </c>
+      <c r="D278" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон iPhone 16 Pro, Pro Max, 256 ГБ, 512 ГБ, 1 ТБ, E-SIM, стекло и чехол в подарок</t>
+        </is>
+      </c>
+      <c r="B279" s="4" t="inlineStr">
+        <is>
+          <t>14 396 200</t>
+        </is>
+      </c>
+      <c r="C279" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-iphone-16-chernyj---1-1682491</t>
+        </is>
+      </c>
+      <c r="D279" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (2 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Honor 400 Pro, 200+50MP, 6000 мА/ч, IP69, 6.67", 120Hz, AMOLED, AI функции</t>
+        </is>
+      </c>
+      <c r="B280" s="4" t="inlineStr">
+        <is>
+          <t>7 967 040</t>
+        </is>
+      </c>
+      <c r="C280" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-honor-400-seryj---3-1838706</t>
+        </is>
+      </c>
+      <c r="D280" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (1 отзыв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A55, 8+256 ГБ, 8+128 ГБ, Super AMOLED 6.6" 120 Гц</t>
+        </is>
+      </c>
+      <c r="B281" s="4" t="inlineStr">
+        <is>
+          <t>5 104 320</t>
+        </is>
+      </c>
+      <c r="C281" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-chernyj---1-1580804</t>
+        </is>
+      </c>
+      <c r="D281" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (1 отзыв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Apple iPhone 13, 128/256 ГБ, 1 SIM/Dual SIM</t>
+        </is>
+      </c>
+      <c r="B282" s="4" t="inlineStr">
+        <is>
+          <t>8 222 200</t>
+        </is>
+      </c>
+      <c r="C282" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-apple-iphone-belyj---5-1454723</t>
+        </is>
+      </c>
+      <c r="D282" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="4" t="inlineStr">
+        <is>
+          <t>HONOR 400 5G (Global, 8/256 GB, MagicOS 9 на Android 15)</t>
+        </is>
+      </c>
+      <c r="B283" s="4" t="inlineStr">
+        <is>
+          <t>4 995 840</t>
+        </is>
+      </c>
+      <c r="C283" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/honor-400-5g-svetlo-sinij---281-1801163</t>
+        </is>
+      </c>
+      <c r="D283" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (1 отзыв)</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Apple iPhone 12, 64/128/256 ГБ, SIM, чехол в подарок</t>
+        </is>
+      </c>
+      <c r="B284" s="4" t="inlineStr">
+        <is>
+          <t>6 859 020</t>
+        </is>
+      </c>
+      <c r="C284" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-apple-iphone-biryuzovyj---124-1702443</t>
+        </is>
+      </c>
+      <c r="D284" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="4" t="inlineStr">
+        <is>
+          <t>Смартфоны Samsung S25 Ultra</t>
+        </is>
+      </c>
+      <c r="B285" s="4" t="inlineStr">
+        <is>
+          <t>15 350 400</t>
+        </is>
+      </c>
+      <c r="C285" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfony-samsung-s25-ultra-chernyj---1-1807758</t>
+        </is>
+      </c>
+      <c r="D285" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Samsung Galaxy A14, 50MП, 5000mAч, NFC, Uzimei зарегистрирован, гарантия 1 год</t>
+        </is>
+      </c>
+      <c r="B286" s="4" t="inlineStr">
+        <is>
+          <t>2 015 040</t>
+        </is>
+      </c>
+      <c r="C286" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-samsung-galaxy-chernyj---1-1734224</t>
+        </is>
+      </c>
+      <c r="D286" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (3 отзыва)</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон W&amp;O X 15 pro max 4/64 ГБ</t>
+        </is>
+      </c>
+      <c r="B287" s="4" t="inlineStr">
+        <is>
+          <t>921 504</t>
+        </is>
+      </c>
+      <c r="C287" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-wo-x-15-pro-max-indigo---251-1827043</t>
+        </is>
+      </c>
+      <c r="D287" s="4" t="inlineStr">
+        <is>
+          <t>Новинка!</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="4" t="inlineStr">
+        <is>
+          <t>Смартфон Xiaomi Redmi Note 13 Pro+ 5G, 12/512 ГБ, 5G, камера 200 МП, NFC +Smart Watch</t>
+        </is>
+      </c>
+      <c r="B288" s="4" t="inlineStr">
+        <is>
+          <t>4 464 000</t>
+        </is>
+      </c>
+      <c r="C288" s="4" t="inlineStr">
+        <is>
+          <t>https://uzum.uz/ru/product/smartfon-xiaomi-redmi-belyj---5-1771492</t>
+        </is>
+      </c>
+      <c r="D288" s="4" t="inlineStr">
+        <is>
+          <t>5.0 (8 отзывов)</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="4" t="inlineStr"/>
+      <c r="B289" s="4" t="inlineStr"/>
+      <c r="C289" s="4" t="inlineStr"/>
+      <c r="D289" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId48"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>